--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486849_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2486849_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>6.7976</v>
+        <v>7.6796</v>
       </c>
       <c r="E2" t="n">
-        <v>2.2207</v>
+        <v>3.0731</v>
       </c>
       <c r="F2" t="n">
-        <v>4.5769</v>
+        <v>4.6065</v>
       </c>
       <c r="G2" t="n">
         <v>1.6564</v>
@@ -610,13 +610,13 @@
         <v>3.0801</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.7008</v>
+        <v>0.1812</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.4147</v>
+        <v>0.4376</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.286</v>
+        <v>-0.2564</v>
       </c>
       <c r="V2" t="n">
         <v>3.9938</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>5.8562</v>
+        <v>6.6336</v>
       </c>
       <c r="E3" t="n">
-        <v>3.1384</v>
+        <v>3.8862</v>
       </c>
       <c r="F3" t="n">
-        <v>2.7177</v>
+        <v>2.7474</v>
       </c>
       <c r="G3" t="n">
         <v>3.4923</v>
@@ -688,13 +688,13 @@
         <v>2.6694</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5458</v>
+        <v>0.2316</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.159</v>
+        <v>0.5888</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.3869</v>
+        <v>-0.3572</v>
       </c>
       <c r="V3" t="n">
         <v>0.2402</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>3.6484</v>
+        <v>3.8756</v>
       </c>
       <c r="E4" t="n">
-        <v>1.903</v>
+        <v>2.1006</v>
       </c>
       <c r="F4" t="n">
-        <v>1.7454</v>
+        <v>1.775</v>
       </c>
       <c r="G4" t="n">
         <v>0.7863</v>
@@ -766,13 +766,13 @@
         <v>1.2321</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.3986</v>
+        <v>-0.1714</v>
       </c>
       <c r="T4" t="n">
-        <v>0.0386</v>
+        <v>0.2362</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.4373</v>
+        <v>-0.4076</v>
       </c>
       <c r="V4" t="n">
         <v>3.0554</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. SIMEUNOVIC</t>
+          <t>L. SAVIKJEVIKJ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9825</v>
+        <v>1.3202</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.2571</v>
+        <v>0.9022</v>
       </c>
       <c r="F5" t="n">
-        <v>2.2395</v>
+        <v>0.418</v>
       </c>
       <c r="G5" t="n">
-        <v>-2.2961</v>
+        <v>-0.2834</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1649</v>
+        <v>0.5189</v>
       </c>
       <c r="I5" t="n">
-        <v>-2.1312</v>
+        <v>-0.8023</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.187</v>
+        <v>1.3053</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9709</v>
+        <v>0.7397</v>
       </c>
       <c r="L5" t="n">
-        <v>-2.158</v>
+        <v>0.5656</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.109</v>
+        <v>-1.5887</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1358</v>
+        <v>-0.2208</v>
       </c>
       <c r="O5" t="n">
-        <v>0.0268</v>
+        <v>-1.3679</v>
       </c>
       <c r="P5" t="n">
-        <v>0.2053</v>
+        <v>0.616</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.2588</v>
+        <v>-0.2053</v>
       </c>
       <c r="R5" t="n">
-        <v>2.4641</v>
+        <v>0.8214</v>
       </c>
       <c r="S5" t="n">
-        <v>2.833</v>
+        <v>-0.4088</v>
       </c>
       <c r="T5" t="n">
-        <v>1.9485</v>
+        <v>-0.1977</v>
       </c>
       <c r="U5" t="n">
-        <v>0.8845</v>
+        <v>-0.211</v>
       </c>
       <c r="V5" t="n">
-        <v>0.2402</v>
+        <v>1.3963</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2402</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>1.3963</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>L. SAVIKJEVIKJ</t>
+          <t>E. MEDINA ROA</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +877,73 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.7627</v>
+        <v>-0.2233</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5225</v>
+        <v>1.6769</v>
       </c>
       <c r="F6" t="n">
-        <v>0.2402</v>
+        <v>-1.9003</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.2834</v>
+        <v>2.8933</v>
       </c>
       <c r="H6" t="n">
-        <v>0.5189</v>
+        <v>3.8508</v>
       </c>
       <c r="I6" t="n">
-        <v>-0.8023</v>
+        <v>-0.9575</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3053</v>
+        <v>3.7769</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7397</v>
+        <v>3.7374</v>
       </c>
       <c r="L6" t="n">
-        <v>0.5656</v>
+        <v>0.0395</v>
       </c>
       <c r="M6" t="n">
-        <v>-1.5887</v>
+        <v>-0.8836000000000001</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.2208</v>
+        <v>0.1134</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.3679</v>
+        <v>-0.997</v>
       </c>
       <c r="P6" t="n">
-        <v>0.616</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2053</v>
+        <v>-2.0534</v>
       </c>
       <c r="R6" t="n">
-        <v>0.8214</v>
+        <v>1.2321</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9663</v>
+        <v>0.062</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.5774</v>
+        <v>-0.0466</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.3889</v>
+        <v>0.1086</v>
       </c>
       <c r="V6" t="n">
-        <v>1.3963</v>
+        <v>-2.3573</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1.3963</v>
+        <v>-2.3573</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>R. GARCIA SALAME</t>
+          <t>E. ARQUES LOPEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +955,73 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.5978</v>
+        <v>-0.3526</v>
       </c>
       <c r="E7" t="n">
-        <v>-3.0901</v>
+        <v>-0.8576</v>
       </c>
       <c r="F7" t="n">
-        <v>2.4923</v>
+        <v>0.505</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.7741</v>
+        <v>-0.3043</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.132</v>
+        <v>-0.3307</v>
       </c>
       <c r="I7" t="n">
-        <v>0.3579</v>
+        <v>0.0264</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.8277</v>
+        <v>0.6736</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.9986</v>
+        <v>-0.418</v>
       </c>
       <c r="L7" t="n">
-        <v>-0.8290999999999999</v>
+        <v>1.0916</v>
       </c>
       <c r="M7" t="n">
-        <v>1.0536</v>
+        <v>-0.9779</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.1335</v>
+        <v>0.0873</v>
       </c>
       <c r="O7" t="n">
-        <v>1.187</v>
+        <v>-1.0652</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.8214</v>
+        <v>0</v>
       </c>
       <c r="Q7" t="n">
-        <v>-3.2855</v>
+        <v>-1.2321</v>
       </c>
       <c r="R7" t="n">
-        <v>2.4641</v>
+        <v>1.2321</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7575</v>
+        <v>-0.2886</v>
       </c>
       <c r="T7" t="n">
-        <v>0.6042</v>
+        <v>0.1587</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1533</v>
+        <v>-0.4473</v>
       </c>
       <c r="V7" t="n">
         <v>0.2402</v>
       </c>
       <c r="W7" t="n">
-        <v>1.4189</v>
+        <v>-0.4579</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1786</v>
+        <v>0.6982</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>E. MEDINA ROA</t>
+          <t>D. SIMEUNOVIC</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1033,73 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.6829</v>
+        <v>-0.477</v>
       </c>
       <c r="E8" t="n">
-        <v>1.336</v>
+        <v>-2.1829</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.0188</v>
+        <v>1.706</v>
       </c>
       <c r="G8" t="n">
-        <v>2.8933</v>
+        <v>-2.2961</v>
       </c>
       <c r="H8" t="n">
-        <v>3.8508</v>
+        <v>-0.1649</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.9575</v>
+        <v>-2.1312</v>
       </c>
       <c r="J8" t="n">
-        <v>3.7769</v>
+        <v>-1.187</v>
       </c>
       <c r="K8" t="n">
-        <v>3.7374</v>
+        <v>0.9709</v>
       </c>
       <c r="L8" t="n">
-        <v>0.0395</v>
+        <v>-2.158</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8836000000000001</v>
+        <v>-1.109</v>
       </c>
       <c r="N8" t="n">
-        <v>0.1134</v>
+        <v>-1.1358</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.997</v>
+        <v>0.0268</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.8214</v>
+        <v>0.2053</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0534</v>
+        <v>-2.2588</v>
       </c>
       <c r="R8" t="n">
-        <v>1.2321</v>
+        <v>2.4641</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3975</v>
+        <v>1.3736</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.3875</v>
+        <v>1.0227</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.01</v>
+        <v>0.3509</v>
       </c>
       <c r="V8" t="n">
-        <v>-2.3573</v>
+        <v>0.2402</v>
       </c>
       <c r="W8" t="n">
+        <v>0.2402</v>
+      </c>
+      <c r="X8" t="n">
         <v>0</v>
-      </c>
-      <c r="X8" t="n">
-        <v>-2.3573</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>E. ARQUES LOPEZ</t>
+          <t>R. GARCIA SALAME</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.7141</v>
+        <v>-0.6258</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.1599</v>
+        <v>-2.9699</v>
       </c>
       <c r="F9" t="n">
-        <v>0.4457</v>
+        <v>2.3441</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3043</v>
+        <v>-0.7741</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.3307</v>
+        <v>-1.132</v>
       </c>
       <c r="I9" t="n">
-        <v>0.0264</v>
+        <v>0.3579</v>
       </c>
       <c r="J9" t="n">
-        <v>0.6736</v>
+        <v>-1.8277</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.418</v>
+        <v>-0.9986</v>
       </c>
       <c r="L9" t="n">
-        <v>1.0916</v>
+        <v>-0.8290999999999999</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9779</v>
+        <v>1.0536</v>
       </c>
       <c r="N9" t="n">
-        <v>0.0873</v>
+        <v>-0.1335</v>
       </c>
       <c r="O9" t="n">
-        <v>-1.0652</v>
+        <v>1.187</v>
       </c>
       <c r="P9" t="n">
-        <v>0</v>
+        <v>-0.8214</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.2321</v>
+        <v>-3.2855</v>
       </c>
       <c r="R9" t="n">
-        <v>1.2321</v>
+        <v>2.4641</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.6501</v>
+        <v>0.7295</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1435</v>
+        <v>0.7244</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5066000000000001</v>
+        <v>0.0051</v>
       </c>
       <c r="V9" t="n">
         <v>0.2402</v>
       </c>
       <c r="W9" t="n">
-        <v>-0.4579</v>
+        <v>1.4189</v>
       </c>
       <c r="X9" t="n">
-        <v>0.6982</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="10">
@@ -1189,13 +1189,13 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.3946</v>
+        <v>-3.1962</v>
       </c>
       <c r="E10" t="n">
-        <v>-2.7205</v>
+        <v>-2.7592</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6741</v>
+        <v>-0.437</v>
       </c>
       <c r="G10" t="n">
         <v>-1.1466</v>
@@ -1234,13 +1234,13 @@
         <v>1.2321</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.706</v>
+        <v>-0.5076000000000001</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.07770000000000001</v>
+        <v>-0.1164</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.6283</v>
+        <v>-0.3912</v>
       </c>
       <c r="V10" t="n">
         <v>-0.7207</v>
@@ -1267,16 +1267,16 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>12.658</v>
+        <v>14.6341</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8930000000000002</v>
+        <v>2.869400000000002</v>
       </c>
       <c r="F11" t="n">
-        <v>11.7648</v>
+        <v>11.7647</v>
       </c>
       <c r="G11" t="n">
-        <v>4.023799999999999</v>
+        <v>4.0238</v>
       </c>
       <c r="H11" t="n">
         <v>13.0742</v>
@@ -1303,7 +1303,7 @@
         <v>-1.6018</v>
       </c>
       <c r="P11" t="n">
-        <v>3.079899999999999</v>
+        <v>3.0799</v>
       </c>
       <c r="Q11" t="n">
         <v>-13.3473</v>
@@ -1312,19 +1312,19 @@
         <v>16.4275</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.7746</v>
+        <v>1.2015</v>
       </c>
       <c r="T11" t="n">
-        <v>0.8314999999999997</v>
+        <v>2.8077</v>
       </c>
       <c r="U11" t="n">
-        <v>-1.6062</v>
+        <v>-1.6061</v>
       </c>
       <c r="V11" t="n">
-        <v>6.3283</v>
+        <v>6.328300000000001</v>
       </c>
       <c r="W11" t="n">
-        <v>6.985500000000001</v>
+        <v>6.9855</v>
       </c>
       <c r="X11" t="n">
         <v>-0.6570000000000001</v>
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>1.9183</v>
+        <v>3.1334</v>
       </c>
       <c r="E12" t="n">
-        <v>1.3678</v>
+        <v>2.4138</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5505</v>
+        <v>0.7196</v>
       </c>
       <c r="G12" t="n">
         <v>2.134</v>
@@ -1390,13 +1390,13 @@
         <v>1.0267</v>
       </c>
       <c r="S12" t="n">
-        <v>-1.1541</v>
+        <v>0.061</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8409</v>
+        <v>0.2051</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.3133</v>
+        <v>-0.1442</v>
       </c>
       <c r="V12" t="n">
         <v>0.9384</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>1.4429</v>
+        <v>2.2379</v>
       </c>
       <c r="E13" t="n">
-        <v>1.0841</v>
+        <v>1.5025</v>
       </c>
       <c r="F13" t="n">
-        <v>0.3588</v>
+        <v>0.7354000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>1.2529</v>
@@ -1468,13 +1468,13 @@
         <v>2.2588</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.6478</v>
+        <v>0.1472</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.1435</v>
+        <v>0.2749</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.5043</v>
+        <v>-0.1277</v>
       </c>
       <c r="V13" t="n">
         <v>1.6591</v>
@@ -1489,7 +1489,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>O. THIAM PEDRERA</t>
+          <t>A. RUBIN DE CELIS FERRANDO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>0.5134</v>
+        <v>0.3872</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.4834</v>
+        <v>-0.3032</v>
       </c>
       <c r="F14" t="n">
-        <v>0.9968</v>
+        <v>0.6904</v>
       </c>
       <c r="G14" t="n">
-        <v>-1.1533</v>
+        <v>1.1561</v>
       </c>
       <c r="H14" t="n">
-        <v>-2.0925</v>
+        <v>-0.0359</v>
       </c>
       <c r="I14" t="n">
-        <v>0.9391</v>
+        <v>1.192</v>
       </c>
       <c r="J14" t="n">
-        <v>-1.541</v>
+        <v>1.1002</v>
       </c>
       <c r="K14" t="n">
-        <v>-1.3168</v>
+        <v>0.3504</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.2241</v>
+        <v>0.7498</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3876</v>
+        <v>0.0559</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.7756</v>
+        <v>-0.3863</v>
       </c>
       <c r="O14" t="n">
-        <v>1.1633</v>
+        <v>0.4422</v>
       </c>
       <c r="P14" t="n">
-        <v>1.0267</v>
+        <v>-0.616</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>-1.0267</v>
       </c>
       <c r="R14" t="n">
-        <v>1.0267</v>
+        <v>0.4107</v>
       </c>
       <c r="S14" t="n">
-        <v>0.3998</v>
+        <v>0.3051</v>
       </c>
       <c r="T14" t="n">
-        <v>0.8173</v>
+        <v>0.08119999999999999</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.4175</v>
+        <v>0.2238</v>
       </c>
       <c r="V14" t="n">
-        <v>0.2402</v>
+        <v>-0.4579</v>
       </c>
       <c r="W14" t="n">
-        <v>0.2402</v>
+        <v>-0.4579</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>A. RUBIN DE CELIS FERRANDO</t>
+          <t>O. THIAM PEDRERA</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>0.4413</v>
+        <v>0.1891</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1986</v>
+        <v>-1.0064</v>
       </c>
       <c r="F15" t="n">
-        <v>0.6398</v>
+        <v>1.1956</v>
       </c>
       <c r="G15" t="n">
-        <v>1.1561</v>
+        <v>-1.1533</v>
       </c>
       <c r="H15" t="n">
-        <v>-0.0359</v>
+        <v>-2.0925</v>
       </c>
       <c r="I15" t="n">
-        <v>1.192</v>
+        <v>0.9391</v>
       </c>
       <c r="J15" t="n">
-        <v>1.1002</v>
+        <v>-1.541</v>
       </c>
       <c r="K15" t="n">
-        <v>0.3504</v>
+        <v>-1.3168</v>
       </c>
       <c r="L15" t="n">
-        <v>0.7498</v>
+        <v>-0.2241</v>
       </c>
       <c r="M15" t="n">
-        <v>0.0559</v>
+        <v>0.3876</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3863</v>
+        <v>-0.7756</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4422</v>
+        <v>1.1633</v>
       </c>
       <c r="P15" t="n">
-        <v>-0.616</v>
+        <v>1.0267</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.0267</v>
+        <v>0</v>
       </c>
       <c r="R15" t="n">
-        <v>0.4107</v>
+        <v>1.0267</v>
       </c>
       <c r="S15" t="n">
-        <v>0.3591</v>
+        <v>0.0755</v>
       </c>
       <c r="T15" t="n">
-        <v>0.1858</v>
+        <v>0.2943</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1733</v>
+        <v>-0.2188</v>
       </c>
       <c r="V15" t="n">
-        <v>-0.4579</v>
+        <v>0.2402</v>
       </c>
       <c r="W15" t="n">
-        <v>-0.4579</v>
+        <v>0.2402</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. FRITZ</t>
+          <t>O. BIESHAAR</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>-1.1907</v>
+        <v>-0.7581</v>
       </c>
       <c r="E16" t="n">
-        <v>-1.9855</v>
+        <v>-1.2704</v>
       </c>
       <c r="F16" t="n">
-        <v>0.7948</v>
+        <v>0.5123</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.5336</v>
+        <v>-2.3772</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.9308999999999999</v>
+        <v>-2.5404</v>
       </c>
       <c r="I16" t="n">
-        <v>0.3973</v>
+        <v>0.1632</v>
       </c>
       <c r="J16" t="n">
-        <v>-1.0393</v>
+        <v>-0.4497</v>
       </c>
       <c r="K16" t="n">
-        <v>-0.4603</v>
+        <v>-0.5416</v>
       </c>
       <c r="L16" t="n">
-        <v>-0.579</v>
+        <v>0.092</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5057</v>
+        <v>-1.9275</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4706</v>
+        <v>-1.9988</v>
       </c>
       <c r="O16" t="n">
-        <v>0.9762999999999999</v>
+        <v>0.0713</v>
       </c>
       <c r="P16" t="n">
-        <v>0.8214</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-2.0534</v>
       </c>
       <c r="R16" t="n">
-        <v>0.8214</v>
+        <v>1.6427</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.2998</v>
+        <v>0.3932</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.248</v>
+        <v>0.0541</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0518</v>
+        <v>0.3391</v>
       </c>
       <c r="V16" t="n">
-        <v>-1.1786</v>
+        <v>1.6366</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.6982</v>
+        <v>1.1786</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.4805</v>
+        <v>0.4579</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M. CARREIRA KREPS</t>
+          <t>H. FIGUEROA ÁLVAREZ</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-1.4984</v>
+        <v>-0.8491</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.499</v>
+        <v>-0.8545</v>
       </c>
       <c r="F17" t="n">
-        <v>-0.9994</v>
+        <v>0.0054</v>
       </c>
       <c r="G17" t="n">
-        <v>1.024</v>
+        <v>-0.1091</v>
       </c>
       <c r="H17" t="n">
-        <v>1.4661</v>
+        <v>-2.7188</v>
       </c>
       <c r="I17" t="n">
-        <v>-0.4422</v>
+        <v>2.6097</v>
       </c>
       <c r="J17" t="n">
-        <v>1.4969</v>
+        <v>1.5633</v>
       </c>
       <c r="K17" t="n">
-        <v>2.1023</v>
+        <v>-0.5806</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.6054</v>
+        <v>2.1438</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.4729</v>
+        <v>-1.6723</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.6362</v>
+        <v>-2.1382</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1632</v>
+        <v>0.4659</v>
       </c>
       <c r="P17" t="n">
-        <v>-2.2588</v>
+        <v>-0.4107</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.0801</v>
+        <v>-2.0534</v>
       </c>
       <c r="R17" t="n">
-        <v>0.8214</v>
+        <v>1.6427</v>
       </c>
       <c r="S17" t="n">
-        <v>1.2641</v>
+        <v>-0.3294</v>
       </c>
       <c r="T17" t="n">
-        <v>1.4333</v>
+        <v>-0.3643</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.1692</v>
+        <v>0.035</v>
       </c>
       <c r="V17" t="n">
-        <v>-1.5277</v>
+        <v>0</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3491</v>
+        <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.1786</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>H. FIGUEROA ÁLVAREZ</t>
+          <t>J. FRITZ</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.6441</v>
+        <v>-1.0652</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2729</v>
+        <v>-1.8809</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.3712</v>
+        <v>0.8157</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.1091</v>
+        <v>-0.5336</v>
       </c>
       <c r="H18" t="n">
-        <v>-2.7188</v>
+        <v>-0.9308999999999999</v>
       </c>
       <c r="I18" t="n">
-        <v>2.6097</v>
+        <v>0.3973</v>
       </c>
       <c r="J18" t="n">
-        <v>1.5633</v>
+        <v>-1.0393</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.5806</v>
+        <v>-0.4603</v>
       </c>
       <c r="L18" t="n">
-        <v>2.1438</v>
+        <v>-0.579</v>
       </c>
       <c r="M18" t="n">
-        <v>-1.6723</v>
+        <v>0.5057</v>
       </c>
       <c r="N18" t="n">
-        <v>-2.1382</v>
+        <v>-0.4706</v>
       </c>
       <c r="O18" t="n">
-        <v>0.4659</v>
+        <v>0.9762999999999999</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.4107</v>
+        <v>0.8214</v>
       </c>
       <c r="Q18" t="n">
-        <v>-2.0534</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>1.6427</v>
+        <v>0.8214</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.1244</v>
+        <v>-0.1743</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7827</v>
+        <v>-0.1434</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3416</v>
+        <v>-0.0309</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-1.1786</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>-0.6982</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.4805</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>O. BIESHAAR</t>
+          <t>M. CARREIRA KREPS</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.9122</v>
+        <v>-2.5252</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.1072</v>
+        <v>-1.7542</v>
       </c>
       <c r="F19" t="n">
-        <v>0.195</v>
+        <v>-0.771</v>
       </c>
       <c r="G19" t="n">
-        <v>-2.3772</v>
+        <v>1.024</v>
       </c>
       <c r="H19" t="n">
-        <v>-2.5404</v>
+        <v>1.4661</v>
       </c>
       <c r="I19" t="n">
+        <v>-0.4422</v>
+      </c>
+      <c r="J19" t="n">
+        <v>1.4969</v>
+      </c>
+      <c r="K19" t="n">
+        <v>2.1023</v>
+      </c>
+      <c r="L19" t="n">
+        <v>-0.6054</v>
+      </c>
+      <c r="M19" t="n">
+        <v>-0.4729</v>
+      </c>
+      <c r="N19" t="n">
+        <v>-0.6362</v>
+      </c>
+      <c r="O19" t="n">
         <v>0.1632</v>
       </c>
-      <c r="J19" t="n">
-        <v>-0.4497</v>
-      </c>
-      <c r="K19" t="n">
-        <v>-0.5416</v>
-      </c>
-      <c r="L19" t="n">
-        <v>0.092</v>
-      </c>
-      <c r="M19" t="n">
-        <v>-1.9275</v>
-      </c>
-      <c r="N19" t="n">
-        <v>-1.9988</v>
-      </c>
-      <c r="O19" t="n">
-        <v>0.0713</v>
-      </c>
       <c r="P19" t="n">
-        <v>-0.4107</v>
+        <v>-2.2588</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.0534</v>
+        <v>-3.0801</v>
       </c>
       <c r="R19" t="n">
-        <v>1.6427</v>
+        <v>0.8214</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.7609</v>
+        <v>0.2373</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.7827</v>
+        <v>0.1781</v>
       </c>
       <c r="U19" t="n">
-        <v>0.0218</v>
+        <v>0.0592</v>
       </c>
       <c r="V19" t="n">
-        <v>1.6366</v>
+        <v>-1.5277</v>
       </c>
       <c r="W19" t="n">
-        <v>1.1786</v>
+        <v>-0.3491</v>
       </c>
       <c r="X19" t="n">
-        <v>0.4579</v>
+        <v>-1.1786</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. BADMUS</t>
+          <t>P. LOPEZ-SANVICENTE RETA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.4038</v>
+        <v>-2.9592</v>
       </c>
       <c r="E20" t="n">
-        <v>-4.5129</v>
+        <v>-1.4908</v>
       </c>
       <c r="F20" t="n">
-        <v>2.1091</v>
+        <v>-1.4684</v>
       </c>
       <c r="G20" t="n">
-        <v>-2.513</v>
+        <v>-2.0653</v>
       </c>
       <c r="H20" t="n">
-        <v>-2.3973</v>
+        <v>-2.2416</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1157</v>
+        <v>0.1763</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.9772</v>
+        <v>-1.3977</v>
       </c>
       <c r="K20" t="n">
-        <v>-1.3718</v>
+        <v>-0.7134</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.6054</v>
+        <v>-0.6843</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.5358000000000001</v>
+        <v>-0.6676</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.0255</v>
+        <v>-1.5282</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4897</v>
+        <v>0.8606</v>
       </c>
       <c r="P20" t="n">
-        <v>-1.4374</v>
+        <v>0.8214</v>
       </c>
       <c r="Q20" t="n">
-        <v>-3.0801</v>
+        <v>0</v>
       </c>
       <c r="R20" t="n">
-        <v>1.6427</v>
+        <v>0.8214</v>
       </c>
       <c r="S20" t="n">
-        <v>2.9429</v>
+        <v>-0.2964</v>
       </c>
       <c r="T20" t="n">
-        <v>1.9408</v>
+        <v>-0.0931</v>
       </c>
       <c r="U20" t="n">
-        <v>1.0021</v>
+        <v>-0.2033</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.3963</v>
+        <v>-1.4189</v>
       </c>
       <c r="W20" t="n">
-        <v>-1.3963</v>
+        <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>0</v>
+        <v>-1.4189</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. LOPEZ-SANVICENTE RETA</t>
+          <t>A. BADMUS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.8999</v>
+        <v>-3.7253</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.4908</v>
+        <v>-5.5589</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.4091</v>
+        <v>1.8336</v>
       </c>
       <c r="G21" t="n">
-        <v>-2.0653</v>
+        <v>-2.513</v>
       </c>
       <c r="H21" t="n">
-        <v>-2.2416</v>
+        <v>-2.3973</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1763</v>
+        <v>-0.1157</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3977</v>
+        <v>-1.9772</v>
       </c>
       <c r="K21" t="n">
-        <v>-0.7134</v>
+        <v>-1.3718</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.6843</v>
+        <v>-0.6054</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.6676</v>
+        <v>-0.5358000000000001</v>
       </c>
       <c r="N21" t="n">
-        <v>-1.5282</v>
+        <v>-1.0255</v>
       </c>
       <c r="O21" t="n">
-        <v>0.8606</v>
+        <v>0.4897</v>
       </c>
       <c r="P21" t="n">
-        <v>0.8214</v>
+        <v>-1.4374</v>
       </c>
       <c r="Q21" t="n">
+        <v>-3.0801</v>
+      </c>
+      <c r="R21" t="n">
+        <v>1.6427</v>
+      </c>
+      <c r="S21" t="n">
+        <v>1.6214</v>
+      </c>
+      <c r="T21" t="n">
+        <v>0.8948</v>
+      </c>
+      <c r="U21" t="n">
+        <v>0.7266</v>
+      </c>
+      <c r="V21" t="n">
+        <v>-1.3963</v>
+      </c>
+      <c r="W21" t="n">
+        <v>-1.3963</v>
+      </c>
+      <c r="X21" t="n">
         <v>0</v>
-      </c>
-      <c r="R21" t="n">
-        <v>0.8214</v>
-      </c>
-      <c r="S21" t="n">
-        <v>-0.2371</v>
-      </c>
-      <c r="T21" t="n">
-        <v>-0.0931</v>
-      </c>
-      <c r="U21" t="n">
-        <v>-0.144</v>
-      </c>
-      <c r="V21" t="n">
-        <v>-1.4189</v>
-      </c>
-      <c r="W21" t="n">
-        <v>0</v>
-      </c>
-      <c r="X21" t="n">
-        <v>-1.4189</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.4245</v>
+        <v>-5.3286</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.6664</v>
+        <v>-1.5618</v>
       </c>
       <c r="F22" t="n">
-        <v>-3.7581</v>
+        <v>-3.7669</v>
       </c>
       <c r="G22" t="n">
         <v>-0.8394</v>
@@ -2170,13 +2170,13 @@
         <v>1.2321</v>
       </c>
       <c r="S22" t="n">
-        <v>0.0329</v>
+        <v>0.1288</v>
       </c>
       <c r="T22" t="n">
-        <v>0.12</v>
+        <v>0.2246</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.08699999999999999</v>
+        <v>-0.0958</v>
       </c>
       <c r="V22" t="n">
         <v>-4.8234</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-12.6577</v>
+        <v>-11.2631</v>
       </c>
       <c r="E23" t="n">
         <v>-11.7648</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.8929999999999998</v>
+        <v>0.5017</v>
       </c>
       <c r="G23" t="n">
         <v>-4.023900000000001</v>
@@ -2248,13 +2248,13 @@
         <v>13.3473</v>
       </c>
       <c r="S23" t="n">
-        <v>0.7746999999999999</v>
+        <v>2.1694</v>
       </c>
       <c r="T23" t="n">
-        <v>1.606300000000001</v>
+        <v>1.6063</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.8314999999999998</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="V23" t="n">
         <v>-6.3285</v>
